--- a/input data.xlsx
+++ b/input data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/oriol_pina_accenture_com/Documents/Desktop/Projectes/04. API/Duty-Cockpit-2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_77159466684255B6E81C4F23E49C36ABCA57EE19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{490D1924-D114-4D27-A85A-FC8097B47620}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_77159466684255B6E81C4F23E49C36ABCA57EE19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EE8E96-B15B-451A-BF34-76018F9F7C26}"/>
   <bookViews>
-    <workbookView xWindow="1584" yWindow="-17280" windowWidth="14400" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1020,8 +1020,8 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="###,000"/>
-    <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1597,7 +1597,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1654,51 +1654,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1939,7 +1906,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <border outline="0">
         <left style="thin">
           <color auto="1"/>
@@ -6318,110 +6285,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C37:D42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="30">
-        <item m="1" x="25"/>
-        <item m="1" x="17"/>
-        <item m="1" x="19"/>
-        <item m="1" x="22"/>
-        <item m="1" x="27"/>
-        <item x="3"/>
-        <item m="1" x="11"/>
-        <item m="1" x="23"/>
-        <item x="8"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item m="1" x="13"/>
-        <item m="1" x="14"/>
-        <item m="1" x="18"/>
-        <item x="0"/>
-        <item m="1" x="21"/>
-        <item m="1" x="26"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item m="1" x="20"/>
-        <item m="1" x="28"/>
-        <item m="1" x="15"/>
-        <item m="1" x="16"/>
-        <item m="1" x="12"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item m="1" x="24"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="2"/>
-        <item m="1" x="8"/>
-        <item x="0"/>
-        <item m="1" x="5"/>
-        <item x="1"/>
-        <item m="1" x="7"/>
-        <item m="1" x="9"/>
-        <item x="3"/>
-        <item m="1" x="10"/>
-        <item m="1" x="6"/>
-        <item m="1" x="4"/>
-        <item m="1" x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of COI" fld="4" subtotal="count" showDataAs="percentOfTotal" baseField="13" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C5:O11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
@@ -6553,6 +6416,110 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Count of COI" fld="4" subtotal="count" showDataAs="percentOfRow" baseField="13" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C37:D42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="30">
+        <item m="1" x="25"/>
+        <item m="1" x="17"/>
+        <item m="1" x="19"/>
+        <item m="1" x="22"/>
+        <item m="1" x="27"/>
+        <item x="3"/>
+        <item m="1" x="11"/>
+        <item m="1" x="23"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="18"/>
+        <item x="0"/>
+        <item m="1" x="21"/>
+        <item m="1" x="26"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item m="1" x="20"/>
+        <item m="1" x="28"/>
+        <item m="1" x="15"/>
+        <item m="1" x="16"/>
+        <item m="1" x="12"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item m="1" x="24"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="2"/>
+        <item m="1" x="8"/>
+        <item x="0"/>
+        <item m="1" x="5"/>
+        <item x="1"/>
+        <item m="1" x="7"/>
+        <item m="1" x="9"/>
+        <item x="3"/>
+        <item m="1" x="10"/>
+        <item m="1" x="6"/>
+        <item m="1" x="4"/>
+        <item m="1" x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of COI" fld="4" subtotal="count" showDataAs="percentOfTotal" baseField="13" baseItem="0" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -12605,7 +12572,7 @@
         <v>34</v>
       </c>
       <c r="L81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -12667,7 +12634,7 @@
         <v>34</v>
       </c>
       <c r="L82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -12729,7 +12696,7 @@
         <v>34</v>
       </c>
       <c r="L83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -12791,7 +12758,7 @@
         <v>34</v>
       </c>
       <c r="L84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -12853,7 +12820,7 @@
         <v>34</v>
       </c>
       <c r="L85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13535,7 +13502,7 @@
         <v>34</v>
       </c>
       <c r="L96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13597,7 +13564,7 @@
         <v>34</v>
       </c>
       <c r="L97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13659,7 +13626,7 @@
         <v>34</v>
       </c>
       <c r="L98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13721,7 +13688,7 @@
         <v>34</v>
       </c>
       <c r="L99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13783,7 +13750,7 @@
         <v>34</v>
       </c>
       <c r="L100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -13845,7 +13812,7 @@
         <v>34</v>
       </c>
       <c r="L101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14155,7 +14122,7 @@
         <v>34</v>
       </c>
       <c r="L106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14217,7 +14184,7 @@
         <v>34</v>
       </c>
       <c r="L107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14279,7 +14246,7 @@
         <v>34</v>
       </c>
       <c r="L108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14341,7 +14308,7 @@
         <v>34</v>
       </c>
       <c r="L109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14403,7 +14370,7 @@
         <v>34</v>
       </c>
       <c r="L110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14465,7 +14432,7 @@
         <v>34</v>
       </c>
       <c r="L111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14527,7 +14494,7 @@
         <v>34</v>
       </c>
       <c r="L112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14589,7 +14556,7 @@
         <v>34</v>
       </c>
       <c r="L113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14651,7 +14618,7 @@
         <v>34</v>
       </c>
       <c r="L114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14713,7 +14680,7 @@
         <v>34</v>
       </c>
       <c r="L115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14775,7 +14742,7 @@
         <v>34</v>
       </c>
       <c r="L116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14837,7 +14804,7 @@
         <v>34</v>
       </c>
       <c r="L117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14899,7 +14866,7 @@
         <v>34</v>
       </c>
       <c r="L118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -14961,7 +14928,7 @@
         <v>34</v>
       </c>
       <c r="L119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -15023,7 +14990,7 @@
         <v>34</v>
       </c>
       <c r="L120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -15085,7 +15052,7 @@
         <v>34</v>
       </c>
       <c r="L121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -15147,7 +15114,7 @@
         <v>34</v>
       </c>
       <c r="L122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -15209,7 +15176,7 @@
         <v>34</v>
       </c>
       <c r="L123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" t="b">
         <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
@@ -19948,44 +19915,44 @@
       <c r="A201" s="30">
         <v>45447</v>
       </c>
-      <c r="B201" s="31" t="s">
+      <c r="B201" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="C201" s="32">
+      <c r="C201" s="26">
         <v>373738</v>
       </c>
-      <c r="D201" s="33" t="s">
+      <c r="D201" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E201" s="34" t="s">
+      <c r="E201" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F201" s="47" t="s">
+      <c r="F201" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G201" s="48">
+      <c r="G201" s="35">
         <v>1175.2978000000001</v>
       </c>
       <c r="H201" t="s">
         <v>34</v>
       </c>
-      <c r="I201" s="44">
-        <v>0</v>
-      </c>
-      <c r="J201" s="48">
+      <c r="I201" s="2">
+        <v>0</v>
+      </c>
+      <c r="J201" s="35">
         <v>97.897599999999997</v>
       </c>
       <c r="K201" t="s">
         <v>34</v>
       </c>
-      <c r="L201" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M201" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N201" s="46" t="str">
+      <c r="L201" t="b">
+        <v>0</v>
+      </c>
+      <c r="M201" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N201" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20001,7 +19968,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O201" s="43">
+      <c r="O201">
         <f>ROW()</f>
         <v>201</v>
       </c>
@@ -20010,44 +19977,44 @@
       <c r="A202" s="30">
         <v>45726</v>
       </c>
-      <c r="B202" s="31" t="s">
+      <c r="B202" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C202" s="32">
+      <c r="C202" s="26">
         <v>373738</v>
       </c>
-      <c r="D202" s="33" t="s">
+      <c r="D202" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E202" s="34" t="s">
+      <c r="E202" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F202" s="47" t="s">
+      <c r="F202" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G202" s="48">
+      <c r="G202" s="35">
         <v>685.38810000000001</v>
       </c>
       <c r="H202" t="s">
         <v>34</v>
       </c>
-      <c r="I202" s="44">
-        <v>0</v>
-      </c>
-      <c r="J202" s="48">
+      <c r="I202" s="2">
+        <v>0</v>
+      </c>
+      <c r="J202" s="35">
         <v>63.324399999999997</v>
       </c>
       <c r="K202" t="s">
         <v>34</v>
       </c>
-      <c r="L202" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M202" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N202" s="46" t="str">
+      <c r="L202" t="b">
+        <v>0</v>
+      </c>
+      <c r="M202" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N202" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20063,7 +20030,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O202" s="43">
+      <c r="O202">
         <f>ROW()</f>
         <v>202</v>
       </c>
@@ -20072,44 +20039,44 @@
       <c r="A203" s="30">
         <v>45821</v>
       </c>
-      <c r="B203" s="31" t="s">
+      <c r="B203" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="C203" s="32">
+      <c r="C203" s="26">
         <v>373738</v>
       </c>
-      <c r="D203" s="33" t="s">
+      <c r="D203" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E203" s="34" t="s">
+      <c r="E203" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F203" s="47" t="s">
+      <c r="F203" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G203" s="48">
+      <c r="G203" s="35">
         <v>238763.51999999999</v>
       </c>
       <c r="H203" t="s">
         <v>34</v>
       </c>
-      <c r="I203" s="44">
-        <v>0</v>
-      </c>
-      <c r="J203" s="48">
+      <c r="I203" s="2">
+        <v>0</v>
+      </c>
+      <c r="J203" s="35">
         <v>22059.8</v>
       </c>
       <c r="K203" t="s">
         <v>34</v>
       </c>
-      <c r="L203" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M203" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N203" s="46" t="str">
+      <c r="L203" t="b">
+        <v>0</v>
+      </c>
+      <c r="M203" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N203" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20125,53 +20092,53 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O203" s="43">
+      <c r="O203">
         <f>ROW()</f>
         <v>203</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A204" s="36">
+      <c r="A204" s="32">
         <v>45870</v>
       </c>
-      <c r="B204" s="37" t="s">
+      <c r="B204" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="C204" s="38">
+      <c r="C204" s="27">
         <v>373738</v>
       </c>
-      <c r="D204" s="39" t="s">
+      <c r="D204" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="E204" s="40" t="s">
+      <c r="E204" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="47" t="s">
+      <c r="F204" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G204" s="48">
+      <c r="G204" s="35">
         <v>1884926.07</v>
       </c>
       <c r="H204" t="s">
         <v>34</v>
       </c>
-      <c r="I204" s="44">
-        <v>0</v>
-      </c>
-      <c r="J204" s="48">
+      <c r="I204" s="2">
+        <v>0</v>
+      </c>
+      <c r="J204" s="35">
         <v>174152.08499999999</v>
       </c>
       <c r="K204" t="s">
         <v>34</v>
       </c>
-      <c r="L204" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M204" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N204" s="46" t="str">
+      <c r="L204" t="b">
+        <v>0</v>
+      </c>
+      <c r="M204" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N204" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20187,7 +20154,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O204" s="43">
+      <c r="O204">
         <f>ROW()</f>
         <v>204</v>
       </c>
@@ -20196,44 +20163,44 @@
       <c r="A205" s="30">
         <v>45383</v>
       </c>
-      <c r="B205" s="31" t="s">
+      <c r="B205" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="C205" s="32">
+      <c r="C205" s="26">
         <v>871079</v>
       </c>
-      <c r="D205" s="33" t="s">
+      <c r="D205" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E205" s="34" t="s">
+      <c r="E205" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F205" s="35" t="s">
+      <c r="F205" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G205" s="42">
+      <c r="G205" s="19">
         <v>146181.166</v>
       </c>
       <c r="H205" t="s">
         <v>34</v>
       </c>
-      <c r="I205" s="44">
-        <v>0</v>
-      </c>
-      <c r="J205" s="45">
+      <c r="I205" s="2">
+        <v>0</v>
+      </c>
+      <c r="J205" s="7">
         <v>7174.5438000000004</v>
       </c>
       <c r="K205" t="s">
         <v>34</v>
       </c>
-      <c r="L205" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M205" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N205" s="46" t="str">
+      <c r="L205" t="b">
+        <v>0</v>
+      </c>
+      <c r="M205" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N205" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20249,7 +20216,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O205" s="43">
+      <c r="O205">
         <f>ROW()</f>
         <v>205</v>
       </c>
@@ -20258,44 +20225,44 @@
       <c r="A206" s="30">
         <v>45413</v>
       </c>
-      <c r="B206" s="31" t="s">
+      <c r="B206" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C206" s="32">
+      <c r="C206" s="26">
         <v>871079</v>
       </c>
-      <c r="D206" s="33" t="s">
+      <c r="D206" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E206" s="34" t="s">
+      <c r="E206" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F206" s="35" t="s">
+      <c r="F206" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G206" s="42">
+      <c r="G206" s="19">
         <v>135721.00599999999</v>
       </c>
       <c r="H206" t="s">
         <v>34</v>
       </c>
-      <c r="I206" s="44">
-        <v>0</v>
-      </c>
-      <c r="J206" s="45">
+      <c r="I206" s="2">
+        <v>0</v>
+      </c>
+      <c r="J206" s="7">
         <v>6786.0502999999999</v>
       </c>
       <c r="K206" t="s">
         <v>34</v>
       </c>
-      <c r="L206" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M206" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N206" s="46" t="str">
+      <c r="L206" t="b">
+        <v>0</v>
+      </c>
+      <c r="M206" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N206" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20311,7 +20278,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O206" s="43">
+      <c r="O206">
         <f>ROW()</f>
         <v>206</v>
       </c>
@@ -20320,44 +20287,44 @@
       <c r="A207" s="30">
         <v>45444</v>
       </c>
-      <c r="B207" s="31" t="s">
+      <c r="B207" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="C207" s="32">
+      <c r="C207" s="26">
         <v>871079</v>
       </c>
-      <c r="D207" s="33" t="s">
+      <c r="D207" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E207" s="34" t="s">
+      <c r="E207" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F207" s="35" t="s">
+      <c r="F207" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G207" s="42">
+      <c r="G207" s="19">
         <v>132158.34299999999</v>
       </c>
       <c r="H207" t="s">
         <v>34</v>
       </c>
-      <c r="I207" s="44">
-        <v>0</v>
-      </c>
-      <c r="J207" s="45">
+      <c r="I207" s="2">
+        <v>0</v>
+      </c>
+      <c r="J207" s="7">
         <v>6607.9171999999999</v>
       </c>
       <c r="K207" t="s">
         <v>34</v>
       </c>
-      <c r="L207" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M207" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N207" s="46" t="str">
+      <c r="L207" t="b">
+        <v>0</v>
+      </c>
+      <c r="M207" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N207" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20373,7 +20340,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O207" s="43">
+      <c r="O207">
         <f>ROW()</f>
         <v>207</v>
       </c>
@@ -20382,44 +20349,44 @@
       <c r="A208" s="30">
         <v>45533</v>
       </c>
-      <c r="B208" s="31" t="s">
+      <c r="B208" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C208" s="32">
+      <c r="C208" s="26">
         <v>871079</v>
       </c>
-      <c r="D208" s="33" t="s">
+      <c r="D208" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E208" s="34" t="s">
+      <c r="E208" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F208" s="35" t="s">
+      <c r="F208" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G208" s="42">
+      <c r="G208" s="19">
         <v>117188.82399999999</v>
       </c>
       <c r="H208" t="s">
         <v>34</v>
       </c>
-      <c r="I208" s="44">
-        <v>0</v>
-      </c>
-      <c r="J208" s="45">
+      <c r="I208" s="2">
+        <v>0</v>
+      </c>
+      <c r="J208" s="7">
         <v>0</v>
       </c>
       <c r="K208" t="s">
         <v>34</v>
       </c>
-      <c r="L208" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M208" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N208" s="46" t="str">
+      <c r="L208" t="b">
+        <v>0</v>
+      </c>
+      <c r="M208" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N208" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20435,7 +20402,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O208" s="43">
+      <c r="O208">
         <f>ROW()</f>
         <v>208</v>
       </c>
@@ -20444,44 +20411,44 @@
       <c r="A209" s="30">
         <v>45596</v>
       </c>
-      <c r="B209" s="31" t="s">
+      <c r="B209" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C209" s="32">
+      <c r="C209" s="26">
         <v>871079</v>
       </c>
-      <c r="D209" s="33" t="s">
+      <c r="D209" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E209" s="34" t="s">
+      <c r="E209" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F209" s="35" t="s">
+      <c r="F209" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G209" s="42">
+      <c r="G209" s="19">
         <v>255987.823</v>
       </c>
       <c r="H209" t="s">
         <v>34</v>
       </c>
-      <c r="I209" s="44">
-        <v>0</v>
-      </c>
-      <c r="J209" s="45">
+      <c r="I209" s="2">
+        <v>0</v>
+      </c>
+      <c r="J209" s="7">
         <v>0</v>
       </c>
       <c r="K209" t="s">
         <v>34</v>
       </c>
-      <c r="L209" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M209" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N209" s="46" t="str">
+      <c r="L209" t="b">
+        <v>0</v>
+      </c>
+      <c r="M209" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N209" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20497,7 +20464,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O209" s="43">
+      <c r="O209">
         <f>ROW()</f>
         <v>209</v>
       </c>
@@ -20506,44 +20473,44 @@
       <c r="A210" s="30">
         <v>45632</v>
       </c>
-      <c r="B210" s="31" t="s">
+      <c r="B210" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C210" s="32">
+      <c r="C210" s="26">
         <v>871079</v>
       </c>
-      <c r="D210" s="33" t="s">
+      <c r="D210" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E210" s="34" t="s">
+      <c r="E210" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F210" s="35" t="s">
+      <c r="F210" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G210" s="42">
+      <c r="G210" s="19">
         <v>125253.72900000001</v>
       </c>
       <c r="H210" t="s">
         <v>34</v>
       </c>
-      <c r="I210" s="44">
-        <v>0</v>
-      </c>
-      <c r="J210" s="45">
+      <c r="I210" s="2">
+        <v>0</v>
+      </c>
+      <c r="J210" s="7">
         <v>0</v>
       </c>
       <c r="K210" t="s">
         <v>34</v>
       </c>
-      <c r="L210" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M210" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N210" s="46" t="str">
+      <c r="L210" t="b">
+        <v>0</v>
+      </c>
+      <c r="M210" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N210" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20559,7 +20526,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O210" s="43">
+      <c r="O210">
         <f>ROW()</f>
         <v>210</v>
       </c>
@@ -20568,44 +20535,44 @@
       <c r="A211" s="30">
         <v>45685</v>
       </c>
-      <c r="B211" s="31" t="s">
+      <c r="B211" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C211" s="32">
+      <c r="C211" s="26">
         <v>871079</v>
       </c>
-      <c r="D211" s="33" t="s">
+      <c r="D211" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E211" s="34" t="s">
+      <c r="E211" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F211" s="35" t="s">
+      <c r="F211" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G211" s="42">
+      <c r="G211" s="19">
         <v>259978.07500000001</v>
       </c>
       <c r="H211" t="s">
         <v>34</v>
       </c>
-      <c r="I211" s="44">
-        <v>0</v>
-      </c>
-      <c r="J211" s="45">
+      <c r="I211" s="2">
+        <v>0</v>
+      </c>
+      <c r="J211" s="7">
         <v>0</v>
       </c>
       <c r="K211" t="s">
         <v>34</v>
       </c>
-      <c r="L211" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M211" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N211" s="46" t="str">
+      <c r="L211" t="b">
+        <v>0</v>
+      </c>
+      <c r="M211" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N211" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20621,7 +20588,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O211" s="43">
+      <c r="O211">
         <f>ROW()</f>
         <v>211</v>
       </c>
@@ -20630,44 +20597,44 @@
       <c r="A212" s="30">
         <v>45712</v>
       </c>
-      <c r="B212" s="31" t="s">
+      <c r="B212" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C212" s="32">
+      <c r="C212" s="26">
         <v>871079</v>
       </c>
-      <c r="D212" s="33" t="s">
+      <c r="D212" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E212" s="34" t="s">
+      <c r="E212" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F212" s="35" t="s">
+      <c r="F212" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="G212" s="42">
+      <c r="G212" s="19">
         <v>270695.212</v>
       </c>
       <c r="H212" t="s">
         <v>34</v>
       </c>
-      <c r="I212" s="44">
-        <v>0</v>
-      </c>
-      <c r="J212" s="45">
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
+      <c r="J212" s="7">
         <v>13245.311600000001</v>
       </c>
       <c r="K212" t="s">
         <v>34</v>
       </c>
-      <c r="L212" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M212" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N212" s="46" t="str">
+      <c r="L212" t="b">
+        <v>0</v>
+      </c>
+      <c r="M212" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N212" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20683,53 +20650,53 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O212" s="43">
+      <c r="O212">
         <f>ROW()</f>
         <v>212</v>
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A213" s="36">
+      <c r="A213" s="32">
         <v>45785</v>
       </c>
-      <c r="B213" s="37" t="s">
+      <c r="B213" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="C213" s="38">
+      <c r="C213" s="27">
         <v>871079</v>
       </c>
-      <c r="D213" s="39" t="s">
+      <c r="D213" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E213" s="40" t="s">
+      <c r="E213" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F213" s="41" t="s">
+      <c r="F213" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="G213" s="42">
+      <c r="G213" s="19">
         <v>126473.504</v>
       </c>
       <c r="H213" t="s">
         <v>34</v>
       </c>
-      <c r="I213" s="44">
-        <v>0</v>
-      </c>
-      <c r="J213" s="45">
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
+      <c r="J213" s="7">
         <v>0</v>
       </c>
       <c r="K213" t="s">
         <v>34</v>
       </c>
-      <c r="L213" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M213" s="46" t="b">
-        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
-        <v>0</v>
-      </c>
-      <c r="N213" s="46" t="str">
+      <c r="L213" t="b">
+        <v>0</v>
+      </c>
+      <c r="M213" t="b">
+        <f>COUNTIFS(Transactions[Invoice Number],Transactions[[#This Row],[Invoice Number]],Transactions[Material Number],Transactions[[#This Row],[Material Number]],Transactions[COO],Transactions[[#This Row],[COO]],Transactions[COI],Transactions[[#This Row],[COI]],Transactions[HS Code],Transactions[[#This Row],[HS Code]],Transactions[Customs Value],Transactions[[#This Row],[Customs Value]],Transactions[Date],Transactions[[#This Row],[Date]],Transactions[Duty Paid],Transactions[[#This Row],[Duty Paid]],Transactions[ID],"&lt;"&amp;Transactions[[#This Row],[ID]])&gt;0</f>
+        <v>0</v>
+      </c>
+      <c r="N213" t="str">
         <f>IF(OR(Transactions[[#This Row],[Date]]&lt;44927,Transactions[[#This Row],[Date]]&gt;47484),"Wrong Date",
 IF(LEN(Transactions[[#This Row],[COO]])&lt;&gt;2,"Wrong COO",
 IF(LEN(Transactions[[#This Row],[COI]])&lt;&gt;2,"Wrong COI",
@@ -20745,7 +20712,7 @@
 ""))))))))))))</f>
         <v/>
       </c>
-      <c r="O213" s="43">
+      <c r="O213">
         <f>ROW()</f>
         <v>213</v>
       </c>
@@ -20787,15 +20754,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="84b7f586-f5a4-47ad-8408-998d44a0a646">
@@ -20804,6 +20762,15 @@
     <TaxCatchAll xmlns="6e280d5c-47a4-49f2-adb9-1bca783c88ca" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21002,20 +20969,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F541856-3460-44A4-8208-9342F3C7ED81}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE39364E-99DC-4C70-8792-50F339DD810F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="84b7f586-f5a4-47ad-8408-998d44a0a646"/>
     <ds:schemaRef ds:uri="6e280d5c-47a4-49f2-adb9-1bca783c88ca"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F541856-3460-44A4-8208-9342F3C7ED81}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
